--- a/forms/trg/Formulir_TRG_rdrg.xlsx
+++ b/forms/trg/Formulir_TRG_rdrg.xlsx
@@ -771,7 +771,7 @@
         </is>
       </c>
       <c r="B24" s="7">
-        <f>COUNTA(Anggota!B5:B27)</f>
+        <f>COUNTA(Anggota!B5:B28)</f>
         <v/>
       </c>
     </row>
@@ -782,7 +782,7 @@
         </is>
       </c>
       <c r="B25" s="7">
-        <f>COUNTA(Anggota!F5:F27)</f>
+        <f>COUNTA(Anggota!F5:F28)</f>
         <v/>
       </c>
     </row>
@@ -808,7 +808,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M27"/>
+  <dimension ref="A1:M28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -913,37 +913,33 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>Prof. Dr. Bahruddin Thalib, drg., M.Kes., Sp.Pros ., Subsp., PKIKG (K).</t>
-        </is>
-      </c>
-      <c r="C5" s="11" t="inlineStr">
-        <is>
-          <t>Lecturers</t>
-        </is>
-      </c>
-      <c r="D5" s="11" t="inlineStr">
-        <is>
-          <t>Hasanuddin University</t>
-        </is>
-      </c>
-      <c r="E5" s="11" t="n"/>
+          <t>Prof. Dr. Asmawati, drg., M.Kes., PBO</t>
+        </is>
+      </c>
+      <c r="C5" s="12" t="n"/>
+      <c r="D5" s="12" t="n"/>
+      <c r="E5" s="11" t="inlineStr">
+        <is>
+          <t>Oral Biology</t>
+        </is>
+      </c>
       <c r="F5" s="12" t="n"/>
       <c r="G5" s="12" t="n"/>
       <c r="H5" s="12" t="n"/>
       <c r="I5" s="12" t="n"/>
       <c r="J5" s="11" t="inlineStr">
         <is>
-          <t>0000-0001-5868-3113</t>
+          <t>0000-0002-1478-8914</t>
         </is>
       </c>
       <c r="K5" s="11" t="inlineStr">
         <is>
-          <t>6023566</t>
+          <t>6022593</t>
         </is>
       </c>
       <c r="L5" s="11" t="inlineStr">
         <is>
-          <t>57197847295</t>
+          <t>57197844600</t>
         </is>
       </c>
       <c r="M5" s="11" t="inlineStr">
@@ -958,12 +954,12 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>Prof. Dr. Nurlindah Hamrun, drg., M.Kes.</t>
+          <t>Prof. Dr. Bahruddin Thalib, drg., M.Kes., Sp.Pros ., Subsp., PKIKG (K).</t>
         </is>
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D6" s="11" t="inlineStr">
@@ -978,17 +974,17 @@
       <c r="I6" s="12" t="n"/>
       <c r="J6" s="11" t="inlineStr">
         <is>
-          <t>0000-0001-6000-7480</t>
+          <t>0000-0001-5868-3113</t>
         </is>
       </c>
       <c r="K6" s="11" t="inlineStr">
         <is>
-          <t>6029500</t>
+          <t>6023566</t>
         </is>
       </c>
       <c r="L6" s="11" t="inlineStr">
         <is>
-          <t>57204107318</t>
+          <t>57197847295</t>
         </is>
       </c>
       <c r="M6" s="11" t="inlineStr">
@@ -1003,12 +999,12 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>dr. Rusdina Bte Ladju, Ph.D</t>
+          <t>Prof. Dr. Nurlindah Hamrun, drg., M.Kes.</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D7" s="11" t="inlineStr">
@@ -1021,9 +1017,21 @@
       <c r="G7" s="12" t="n"/>
       <c r="H7" s="12" t="n"/>
       <c r="I7" s="12" t="n"/>
-      <c r="J7" s="12" t="n"/>
-      <c r="K7" s="12" t="n"/>
-      <c r="L7" s="12" t="n"/>
+      <c r="J7" s="11" t="inlineStr">
+        <is>
+          <t>0000-0001-6000-7480</t>
+        </is>
+      </c>
+      <c r="K7" s="11" t="inlineStr">
+        <is>
+          <t>6029500</t>
+        </is>
+      </c>
+      <c r="L7" s="11" t="inlineStr">
+        <is>
+          <t>57204107318</t>
+        </is>
+      </c>
       <c r="M7" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1036,12 +1044,12 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>Prof. Yulia Yusrini Djabir, S.Si., MBM.Sc., M.Si., Ph.D., Apt</t>
+          <t>dr. Rusdina Bte Ladju, Ph.D</t>
         </is>
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D8" s="11" t="inlineStr">
@@ -1069,12 +1077,12 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>Rafikah Hasyim, drg., M. Biomed.</t>
+          <t>Prof. Yulia Yusrini Djabir, S.Si., MBM.Sc., M.Si., Ph.D., Apt</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D9" s="11" t="inlineStr">
@@ -1088,16 +1096,8 @@
       <c r="H9" s="12" t="n"/>
       <c r="I9" s="12" t="n"/>
       <c r="J9" s="12" t="n"/>
-      <c r="K9" s="11" t="inlineStr">
-        <is>
-          <t>6015347</t>
-        </is>
-      </c>
-      <c r="L9" s="11" t="inlineStr">
-        <is>
-          <t>57197845985</t>
-        </is>
-      </c>
+      <c r="K9" s="12" t="n"/>
+      <c r="L9" s="12" t="n"/>
       <c r="M9" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1110,12 +1110,12 @@
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>Al\' Qarama Mahardhika Thalib, drg., MARS.</t>
+          <t>Rafikah Hasyim, drg., M. Biomed.</t>
         </is>
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D10" s="11" t="inlineStr">
@@ -1131,12 +1131,12 @@
       <c r="J10" s="12" t="n"/>
       <c r="K10" s="11" t="inlineStr">
         <is>
-          <t>6760832</t>
+          <t>6015347</t>
         </is>
       </c>
       <c r="L10" s="11" t="inlineStr">
         <is>
-          <t>57217080888</t>
+          <t>57197845985</t>
         </is>
       </c>
       <c r="M10" s="11" t="inlineStr">
@@ -1151,17 +1151,17 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>Takashi SAITO, DDS, PhD</t>
+          <t>Al\' Qarama Mahardhika Thalib, drg., MARS.</t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D11" s="11" t="inlineStr">
         <is>
-          <t>School of Dentistry, Health Sciences University of Hokkaido</t>
+          <t>Hasanuddin University</t>
         </is>
       </c>
       <c r="E11" s="11" t="n"/>
@@ -1170,8 +1170,16 @@
       <c r="H11" s="12" t="n"/>
       <c r="I11" s="12" t="n"/>
       <c r="J11" s="12" t="n"/>
-      <c r="K11" s="12" t="n"/>
-      <c r="L11" s="12" t="n"/>
+      <c r="K11" s="11" t="inlineStr">
+        <is>
+          <t>6760832</t>
+        </is>
+      </c>
+      <c r="L11" s="11" t="inlineStr">
+        <is>
+          <t>57217080888</t>
+        </is>
+      </c>
       <c r="M11" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1184,17 +1192,17 @@
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>Muhammad Fadil Hidayat, drg., Sp.RKG</t>
+          <t>Takashi SAITO, DDS, PhD</t>
         </is>
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D12" s="11" t="inlineStr">
         <is>
-          <t>Hasanuddin University</t>
+          <t>School of Dentistry, Health Sciences University of Hokkaido</t>
         </is>
       </c>
       <c r="E12" s="11" t="n"/>
@@ -1217,12 +1225,12 @@
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>Kurnia Fatwati, drg., M.KG</t>
+          <t>Muhammad Fadil Hidayat, drg., Sp.RKG</t>
         </is>
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D13" s="11" t="inlineStr">
@@ -1250,12 +1258,12 @@
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>Aulia Ufaira Nada Zahirah</t>
+          <t>Kurnia Fatwati, drg., M.KG</t>
         </is>
       </c>
       <c r="C14" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D14" s="11" t="inlineStr">
@@ -1283,12 +1291,12 @@
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>Muthi\'ah Nasywa</t>
+          <t>Aulia Ufaira Nada Zahirah</t>
         </is>
       </c>
       <c r="C15" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D15" s="11" t="inlineStr">
@@ -1314,10 +1322,26 @@
       <c r="A16" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="B16" s="12" t="n"/>
-      <c r="C16" s="12" t="n"/>
-      <c r="D16" s="12" t="n"/>
-      <c r="E16" s="11" t="n"/>
+      <c r="B16" s="11" t="inlineStr">
+        <is>
+          <t>Muthi\'ah Nasywa</t>
+        </is>
+      </c>
+      <c r="C16" s="11" t="inlineStr">
+        <is>
+          <t>Student</t>
+        </is>
+      </c>
+      <c r="D16" s="11" t="inlineStr">
+        <is>
+          <t>Hasanuddin University</t>
+        </is>
+      </c>
+      <c r="E16" s="11" t="inlineStr">
+        <is>
+          <t>The Regenerative Dentistry Research Group is dedicated to advancing innovation and sustainability in dental science. Our research focuses on developing cutting-edge regenerative therapies, biomaterials, and technologies to enhance oral health and improve patient outcomes. Through interdisciplinary collaboration and scientific excellence, we strive to shape the future of dentistry with sustainable and innovative solutions.</t>
+        </is>
+      </c>
       <c r="F16" s="12" t="n"/>
       <c r="G16" s="12" t="n"/>
       <c r="H16" s="12" t="n"/>
@@ -1325,7 +1349,11 @@
       <c r="J16" s="12" t="n"/>
       <c r="K16" s="12" t="n"/>
       <c r="L16" s="12" t="n"/>
-      <c r="M16" s="12" t="n"/>
+      <c r="M16" s="11" t="inlineStr">
+        <is>
+          <t>Aktif</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="n">
@@ -1514,15 +1542,32 @@
       <c r="L27" s="12" t="n"/>
       <c r="M27" s="12" t="n"/>
     </row>
+    <row r="28">
+      <c r="A28" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="B28" s="12" t="n"/>
+      <c r="C28" s="12" t="n"/>
+      <c r="D28" s="12" t="n"/>
+      <c r="E28" s="11" t="n"/>
+      <c r="F28" s="12" t="n"/>
+      <c r="G28" s="12" t="n"/>
+      <c r="H28" s="12" t="n"/>
+      <c r="I28" s="12" t="n"/>
+      <c r="J28" s="12" t="n"/>
+      <c r="K28" s="12" t="n"/>
+      <c r="L28" s="12" t="n"/>
+      <c r="M28" s="12" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:M2"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="F5:H27" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F5:H28" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$A$2:$A$39</formula1>
     </dataValidation>
-    <dataValidation sqref="M5:M27" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="M5:M28" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$C$2:$C$3</formula1>
     </dataValidation>
   </dataValidations>

--- a/forms/trg/Formulir_TRG_rdrg.xlsx
+++ b/forms/trg/Formulir_TRG_rdrg.xlsx
@@ -916,7 +916,11 @@
           <t>Prof. Dr. Asmawati, drg., M.Kes., PBO</t>
         </is>
       </c>
-      <c r="C5" s="12" t="n"/>
+      <c r="C5" s="11" t="inlineStr">
+        <is>
+          <t>Leader</t>
+        </is>
+      </c>
       <c r="D5" s="12" t="n"/>
       <c r="E5" s="11" t="inlineStr">
         <is>
